--- a/Model_Results.xlsx
+++ b/Model_Results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,50 +436,60 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Basic Materials_logp</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Communication Services_logp</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Consumer Cyclical_logp</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Consumer Defensive_logp</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Energy_logp</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Financial Services_logp</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Healthcare_logp</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Industrials_logp</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Real Estate_logp</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Technology_logp</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Utilities_logp</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Income Elasticity</t>
         </is>
@@ -488,334 +498,474 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Communication Services_w</t>
+          <t>Basic Materials_w</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.961593634904927</v>
+        <v>-3.004620581227543</v>
       </c>
       <c r="C2" t="n">
-        <v>7.560572145170615</v>
+        <v>-3.511598547632621</v>
       </c>
       <c r="D2" t="n">
-        <v>-6.323927474100405</v>
+        <v>8.283203239793195</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.871506136886376</v>
+        <v>-7.15729076079901</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.582724483239526</v>
+        <v>1.470993002329774</v>
       </c>
       <c r="G2" t="n">
-        <v>24.77758530738785</v>
+        <v>-0.7572236643738662</v>
       </c>
       <c r="H2" t="n">
-        <v>1.892539713144578</v>
+        <v>5.313547118529483</v>
       </c>
       <c r="I2" t="n">
-        <v>-19.10976428574459</v>
+        <v>25.85214869570722</v>
       </c>
       <c r="J2" t="n">
-        <v>-4.840295980560716</v>
+        <v>-4.983430435344613</v>
       </c>
       <c r="K2" t="n">
-        <v>1.312276668508785</v>
+        <v>-24.94283523000404</v>
+      </c>
+      <c r="L2" t="n">
+        <v>10.72338140619839</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.474466753631385</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Consumer Cyclical_w</t>
+          <t>Communication Services_w</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.3253120099840196</v>
+        <v>12.55854316291175</v>
       </c>
       <c r="C3" t="n">
-        <v>-7.845000003903461</v>
+        <v>4.354951888222494</v>
       </c>
       <c r="D3" t="n">
-        <v>-4.95678378252504</v>
+        <v>13.68348216165669</v>
       </c>
       <c r="E3" t="n">
-        <v>-7.194907201433814</v>
+        <v>4.049670393289015</v>
       </c>
       <c r="F3" t="n">
-        <v>6.454995503206</v>
+        <v>-2.58137343095921</v>
       </c>
       <c r="G3" t="n">
-        <v>9.240274021941795</v>
+        <v>1.627136241573609</v>
       </c>
       <c r="H3" t="n">
-        <v>4.870305164229199</v>
+        <v>16.59758416222769</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3770331590422121</v>
+        <v>-14.82696902434705</v>
       </c>
       <c r="J3" t="n">
-        <v>-9.414215005594668</v>
+        <v>-2.900283441615785</v>
       </c>
       <c r="K3" t="n">
-        <v>1.098746018991029</v>
+        <v>-17.84759228066283</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-2.345708125156694</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.5142832025272994</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Consumer Defensive_w</t>
+          <t>Consumer Cyclical_w</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1459671928001354</v>
+        <v>0.6691712271750476</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.426559915423015</v>
+        <v>0.3134216500870254</v>
       </c>
       <c r="D4" t="n">
-        <v>9.978440054464706</v>
+        <v>0.08278708597663779</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1861238508643871</v>
+        <v>1.923483602250765</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5339833025226757</v>
+        <v>-7.738006046119059</v>
       </c>
       <c r="G4" t="n">
-        <v>-11.579397453361</v>
+        <v>7.856956851815958</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.888968382658014</v>
+        <v>5.367531671062758</v>
       </c>
       <c r="I4" t="n">
-        <v>3.23577632098232</v>
+        <v>5.875186172281665</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4121912551498772</v>
+        <v>-7.592114735275757</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6671247348085988</v>
+        <v>-7.377200843640026</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-2.785336336812535</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.039040482378988</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Energy_w</t>
+          <t>Consumer Defensive_w</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2.886813002052761</v>
+        <v>-3.032955223871702</v>
       </c>
       <c r="C5" t="n">
-        <v>-27.22562494547507</v>
+        <v>1.073201322146748</v>
       </c>
       <c r="D5" t="n">
-        <v>68.37228033469079</v>
+        <v>-2.437018220762914</v>
       </c>
       <c r="E5" t="n">
-        <v>17.62049509544575</v>
+        <v>8.721547324359539</v>
       </c>
       <c r="F5" t="n">
-        <v>25.83563903066374</v>
+        <v>-0.3393295613268451</v>
       </c>
       <c r="G5" t="n">
-        <v>2.639798842784832</v>
+        <v>0.47625928192113</v>
       </c>
       <c r="H5" t="n">
-        <v>-42.38876266040169</v>
+        <v>-7.076859225030902</v>
       </c>
       <c r="I5" t="n">
-        <v>19.27438525778473</v>
+        <v>0.9576837250541028</v>
       </c>
       <c r="J5" t="n">
-        <v>-30.51941478226918</v>
+        <v>1.370357070201787</v>
       </c>
       <c r="K5" t="n">
-        <v>1.109294154388159</v>
+        <v>0.7344917419272289</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-1.898424252459305</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.8214724034623883</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Financial Services_w</t>
+          <t>Energy_w</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3963819978607943</v>
+        <v>-2.495323584586924</v>
       </c>
       <c r="C6" t="n">
-        <v>8.365113027236456</v>
+        <v>-1.648909056887964</v>
       </c>
       <c r="D6" t="n">
-        <v>-14.59059676341466</v>
+        <v>-21.16795894983403</v>
       </c>
       <c r="E6" t="n">
-        <v>1.418340066939757</v>
+        <v>47.74065722358795</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.593628393508556</v>
+        <v>12.95286961187997</v>
       </c>
       <c r="G6" t="n">
-        <v>11.88201595763404</v>
+        <v>15.05656011385123</v>
       </c>
       <c r="H6" t="n">
-        <v>6.948757392404882</v>
+        <v>-7.773123076887781</v>
       </c>
       <c r="I6" t="n">
-        <v>-10.75024400430331</v>
+        <v>-27.2164857552436</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3617535843044073</v>
+        <v>-6.253369076044149</v>
       </c>
       <c r="K6" t="n">
-        <v>1.40031042011428</v>
+        <v>17.90943156623093</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-6.287137357031475</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.6879010657123013</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Healthcare_w</t>
+          <t>Financial Services_w</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.38851890307094</v>
+        <v>-1.864453031748404</v>
       </c>
       <c r="C7" t="n">
-        <v>-15.80553068851908</v>
+        <v>0.099772984303717</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.630637716947323</v>
+        <v>3.035355984084664</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.68253058871752</v>
+        <v>-7.448077400054834</v>
       </c>
       <c r="F7" t="n">
-        <v>-13.06867922327431</v>
+        <v>0.7686771674333108</v>
       </c>
       <c r="G7" t="n">
-        <v>-16.02286120418414</v>
+        <v>-0.6717617400339735</v>
       </c>
       <c r="H7" t="n">
-        <v>17.38714007703728</v>
+        <v>1.013124333756558</v>
       </c>
       <c r="I7" t="n">
-        <v>6.362988521499091</v>
+        <v>5.43905326109656</v>
       </c>
       <c r="J7" t="n">
-        <v>16.55242640916319</v>
+        <v>-1.019600006322408</v>
       </c>
       <c r="K7" t="n">
-        <v>1.120249498344938</v>
+        <v>-2.88771787370211</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.636532247666488</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.095963204923485</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Industrials_w</t>
+          <t>Healthcare_w</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-3.620283080142829</v>
+        <v>21.08568501211515</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.287118688664386</v>
+        <v>7.62168026049577</v>
       </c>
       <c r="D8" t="n">
-        <v>-7.701524310731392</v>
+        <v>-14.07683680834282</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.470832627080555</v>
+        <v>-4.179214640471419</v>
       </c>
       <c r="F8" t="n">
-        <v>6.486200782317927</v>
+        <v>-5.803052450012679</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1962188874189605</v>
+        <v>-10.18886816672085</v>
       </c>
       <c r="H8" t="n">
-        <v>6.116202898215921</v>
+        <v>-2.497822616437733</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.562766830391948</v>
+        <v>1.261398080511624</v>
       </c>
       <c r="J8" t="n">
-        <v>1.295091334669347</v>
+        <v>2.29927170548075</v>
       </c>
       <c r="K8" t="n">
-        <v>1.153365886545392</v>
+        <v>-0.115030851407839</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4.668891104459498</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.151166910365928</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Technology_w</t>
+          <t>Industrials_w</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-2.485066827519421</v>
+        <v>-13.34123116728363</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5861885372107588</v>
+        <v>-6.603436082226744</v>
       </c>
       <c r="D9" t="n">
-        <v>-10.91309215996096</v>
+        <v>12.36639059146044</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.969060628983558</v>
+        <v>2.352627756265133</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.565321299369172</v>
+        <v>1.087101359231593</v>
       </c>
       <c r="G9" t="n">
-        <v>12.23427818561315</v>
+        <v>4.229035315072735</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.656278018342014</v>
+        <v>-3.2268831971907</v>
       </c>
       <c r="I9" t="n">
-        <v>7.81232912913574</v>
+        <v>20.15235343253138</v>
       </c>
       <c r="J9" t="n">
-        <v>2.378677769759519</v>
+        <v>-8.906308611885141</v>
       </c>
       <c r="K9" t="n">
-        <v>1.132008853390167</v>
+        <v>-18.83160901666796</v>
+      </c>
+      <c r="L9" t="n">
+        <v>16.71244949926973</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.070071831379565</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Real Estate_w</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>6.10404520313707</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-4.148675223538373</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.119158709338684</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-29.3650750961773</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-10.05756052674533</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.506968461634092</v>
+      </c>
+      <c r="H10" t="n">
+        <v>14.82521438830311</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6.607910328224172</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.103343104817765</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.08596877947722339</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-4.038747893121197</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.172802635474459</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Technology_w</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>7.770188628978522</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-3.176531682837592</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5767730504587039</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-10.6892522687843</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-2.154357340965785</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-3.074313744807108</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10.64972484130644</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-11.64052322223138</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.131709315396447</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.422125143704625</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-1.841169144613592</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.22575059800539</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Utilities_w</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>-6.574986808937768</v>
-      </c>
-      <c r="C10" t="n">
-        <v>40.07796053236717</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-30.2341581814757</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-3.663874128419294</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-20.50046521931878</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-32.97547477039756</v>
-      </c>
-      <c r="H10" t="n">
-        <v>11.71906381636986</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-3.885670949919827</v>
-      </c>
-      <c r="J10" t="n">
-        <v>24.49729258398704</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-8.993376235091349</v>
+      <c r="B12" t="n">
+        <v>-24.44904964559933</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5.626122487867539</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.772980574848133</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-5.949076133465537</v>
+      </c>
+      <c r="F12" t="n">
+        <v>12.39403821525426</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-16.06074894993296</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-33.19203839963892</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-12.46175569358469</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20.7504251105911</v>
+      </c>
+      <c r="K12" t="n">
+        <v>44.02190642369925</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-14.54473114839931</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-10.25291908786119</v>
       </c>
     </row>
   </sheetData>
